--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/2-Decision-Tables/SmartRules.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/2-Decision-Tables/SmartRules.xlsx
@@ -2020,9 +2020,9 @@
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B27:I27"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B27:I27"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
@@ -2811,8 +2811,8 @@
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B62:F62"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="C57:D57"/>
@@ -2833,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I50"/>
+  <dimension ref="B2:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -3035,111 +3035,114 @@
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Method Integer GreetingWordCount(Integer hour)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Integer GreetingWordCount(Integer hour)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>return length(GreetingWords(hour));</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>= length(GreetingWords(hour))</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Test GreetingWordCount GreetingWordCountTest</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>hour</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Distinct Words</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C33" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="B34" s="2" t="inlineStr">
+    <row r="35" ht="16.5" customHeight="1">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>"Collect as &lt;KeyType&gt; and &lt;ValueType&gt; Map" collects a Map: the first return column gives the keys, the second one the values.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>SmartRules Collect as String and Integer Map ShopStock(String shop)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Downtown</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3150,137 +3153,172 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>pear</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="7" t="inlineStr">
         <is>
+          <t>Downtown</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>pear</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
           <t>Airport</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>fig</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D41" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Method Integer StockOf(String shop, String product)</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>return (Integer) ShopStock(shop).get(product);</t>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Integer StockOf(String shop, String product)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>= (Integer) ShopStock(shop).get(product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Test StockOf StockOfTest</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="B46" s="9" t="inlineStr">
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>shop</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Downtown</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>pear</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>fig</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>Downtown</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>pear</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>Airport</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>fig</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Airport</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>pear</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
